--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.88519579602337</v>
+        <v>6.481344316853797</v>
       </c>
       <c r="D2" t="n">
-        <v>17.620206853059</v>
+        <v>2.863283613622087</v>
       </c>
       <c r="E2" t="n">
-        <v>12.60401530637472</v>
+        <v>2.048152487285892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9711874451958771</v>
+        <v>0.1578179598443301</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.67716518327392</v>
+        <v>2.385039342282012</v>
       </c>
       <c r="D3" t="n">
-        <v>15.67783196266724</v>
+        <v>2.547647693933427</v>
       </c>
       <c r="E3" t="n">
-        <v>12.60401530637472</v>
+        <v>2.048152487285892</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9711874451958771</v>
+        <v>0.1578179598443301</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
